--- a/testakten/statusfeststellung-gmbh-geschaeftsfuehrer-minderheit-erlangen/31_beitragsberechnung_rv_kv_pv_alv.xlsx
+++ b/testakten/statusfeststellung-gmbh-geschaeftsfuehrer-minderheit-erlangen/31_beitragsberechnung_rv_kv_pv_alv.xlsx
@@ -432,7 +432,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Bruttoverguetung EUR/Monat</t>
+          <t>Bruttovergütung EUR/Monat</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -594,6 +594,7 @@
         <v>193.7</v>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -604,7 +605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Die Beitragsbemessungsgrenzen sind bundeseinheitliche Werte laut Sozialversicherungs-Rechengroessenverordnung fuer die jeweiligen Jahre. Fuer 2026 werden vorlaeufige Werte verwendet, endgueltige Werte stehen zum Zeitpunkt der Aktenanlage noch aus.</t>
+          <t>Die Beitragsbemessungsgrenzen sind bundeseinheitliche Werte laut Sozialversicherungs-Rechengrößenverordnung für die jeweiligen Jahre. Für 2026 werden vorläufige Werte verwendet, endgültige Werte stehen zum Zeitpunkt der Aktenanlage noch aus.</t>
         </is>
       </c>
     </row>
@@ -645,12 +646,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Verjaehrungsfrist Paragraf 25 SGB IV</t>
+          <t>Verjährungsfrist Paragraf 25 SGB IV</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Verjaehrung tritt ein zum</t>
+          <t>Verjährung tritt ein zum</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -686,7 +687,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nicht verjaehrt, sofern kein Vorsatz</t>
+          <t>Nicht verjährt, sofern kein Vorsatz</t>
         </is>
       </c>
     </row>
@@ -717,7 +718,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nicht verjaehrt</t>
+          <t>Nicht verjährt</t>
         </is>
       </c>
     </row>
@@ -748,7 +749,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nicht verjaehrt</t>
+          <t>Nicht verjährt</t>
         </is>
       </c>
     </row>
@@ -779,34 +780,34 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nicht verjaehrt, Verfahren laeuft</t>
-        </is>
-      </c>
-    </row>
+          <t>Nicht verjährt, Verfahren läuft</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>Gesamtsumme Hauptforderung</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
       <c r="D7">
         <f>SUM(D2:D5)</f>
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pruefhinweis</t>
+          <t>Prüfhinweis</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Die vierjaehrige Regelverjaehrung nach Paragraf 25 Absatz 1 SGB IV gilt, solange kein bedingter Vorsatz vorliegt; bei Vorsatz betruege die Frist 30 Jahre. Die Gesellschaft hatte sich auf eine rechtliche Einschaetzung ihres damaligen Beraters gestuetzt, sodass Vorsatz von der Kanzlei bestritten wird.</t>
+          <t>Die vierjährige Regelverjährung nach Paragraf 25 Absatz 1 SGB IV gilt, solange kein bedingter Vorsatz vorliegt; bei Vorsatz betrüge die Frist 30 Jahre. Die Gesellschaft hatte sich auf eine rechtliche Einschätzung ihres damaligen Beraters gestützt, sodass Vorsatz von der Kanzlei bestritten wird.</t>
         </is>
       </c>
     </row>
@@ -832,12 +833,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Rueckstand EUR (gerundet)</t>
+          <t>Rückstand EUR (gerundet)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Saeumniszuschlag Prozent pro Monat</t>
+          <t>Säumniszuschlag Prozent pro Monat</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -867,12 +868,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>erst ab Kenntnis, siehe Anhoerung 18.11.2025</t>
+          <t>erst ab Kenntnis, siehe Anhörung 18.11.2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gutglaeubigkeit wird von der Kanzlei geltend gemacht</t>
+          <t>Gutgläubigkeit wird von der Kanzlei geltend gemacht</t>
         </is>
       </c>
     </row>
@@ -897,7 +898,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>unstreitig, falls Bescheid bestandskraeftig wird</t>
+          <t>unstreitig, falls Bescheid bestandskräftig wird</t>
         </is>
       </c>
     </row>
